--- a/dashboard_data_template.xlsx
+++ b/dashboard_data_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marco Pichardo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F553438D-5C10-47FF-8F7C-60038FA66A3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78050869-13EA-4D45-AE37-5CCF1F1CFA02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="600" yWindow="-16320" windowWidth="28320" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dbMegara" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="160">
   <si>
     <t>tema</t>
   </si>
@@ -89,9 +89,6 @@
     <t>27/05/2026</t>
   </si>
   <si>
-    <t>24/3/2026</t>
-  </si>
-  <si>
     <t>- S3 alineará internamente</t>
   </si>
   <si>
@@ -333,9 +330,6 @@
   </si>
   <si>
     <t>Creacion Assincronos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A la espera de instrucciones por parte de Guilherme </t>
   </si>
   <si>
     <t>Esperando respuesta de Guilherme</t>
@@ -396,24 +390,6 @@
     <t>Verificacion de logica</t>
   </si>
   <si>
-    <t>A la espera de resppuesta de s3</t>
-  </si>
-  <si>
-    <t>Megara</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S3 / VERMEG </t>
-  </si>
-  <si>
-    <t>Modulos</t>
-  </si>
-  <si>
-    <t>Caida de modulos MEACUSTODY</t>
-  </si>
-  <si>
-    <t>S3 verificará con proovedor</t>
-  </si>
-  <si>
     <t>Liberado en UAT</t>
   </si>
   <si>
@@ -423,21 +399,6 @@
     <t>Interfaces</t>
   </si>
   <si>
-    <t>Se ha compartido con S3 la lgica implementada para obtencion de valor "Valor Liquido" y Jur/prejuizo</t>
-  </si>
-  <si>
-    <t>Duplicados en mapeo de sac_stat_fu_cotativo_t (4000)</t>
-  </si>
-  <si>
-    <t>Es necesaria la validacion del codigo de mapeo</t>
-  </si>
-  <si>
-    <t>Duplicados</t>
-  </si>
-  <si>
-    <t>Mapementos</t>
-  </si>
-  <si>
     <t>NFQ / S3 / VERMEG</t>
   </si>
   <si>
@@ -448,9 +409,6 @@
   </si>
   <si>
     <t>S3 se encuentra en alaisis con VERMEG</t>
-  </si>
-  <si>
-    <t>Client Instruction</t>
   </si>
   <si>
     <t>Valores de campos demsiado grandes impiden insercion en tablas de la ddbb</t>
@@ -475,29 +433,98 @@
     <t>Asset</t>
   </si>
   <si>
-    <t>En desarrollo de nueva estructrua de xsd</t>
-  </si>
-  <si>
-    <t>Cambio de tipo de dato para todas las interfaces</t>
-  </si>
-  <si>
-    <t>NFQ terminará desarrollo</t>
-  </si>
-  <si>
     <t xml:space="preserve">En curso </t>
   </si>
   <si>
     <t>NavBankBalance</t>
   </si>
   <si>
-    <t>En desarrollo de nueva interfaz</t>
+    <t>Desarrollo listo en UAT</t>
+  </si>
+  <si>
+    <t>Client Instruction Tamaño de campos</t>
+  </si>
+  <si>
+    <t>Client Instruction (Pk "duplicada")</t>
+  </si>
+  <si>
+    <t>En tratamiento para correccion de alores duplicados en mapeos a pedido de Meneses</t>
+  </si>
+  <si>
+    <t>NFQ entregará el dia de hoy</t>
+  </si>
+  <si>
+    <t>Optimizacion de Informe</t>
+  </si>
+  <si>
+    <t>El dia de hoy se alinearaá con Marcela el mejor momento para validacion de datos y despliegue</t>
+  </si>
+  <si>
+    <t>Se validará y desplegará</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En desarrollo de los informes </t>
+  </si>
+  <si>
+    <t>Se ha revisado con Menses la logica impementada en el informe</t>
+  </si>
+  <si>
+    <t>Dividendos Juros Aporpiados</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No iniciado </t>
+  </si>
+  <si>
+    <t>En analisis de la mejor estrategia a llevar a cabo</t>
+  </si>
+  <si>
+    <t>Fue recibido por parte de S3 apuntamientos de divergencia de informacion</t>
+  </si>
+  <si>
+    <t>NFQ se encuentra en analisis de incidencia</t>
+  </si>
+  <si>
+    <t>Rundeck</t>
+  </si>
+  <si>
+    <t>S3 / NTT / NFQ</t>
+  </si>
+  <si>
+    <t>Tiempos de carga</t>
+  </si>
+  <si>
+    <t>Los tiempos de carga vuelven a encontrarse estables</t>
+  </si>
+  <si>
+    <t>Qlik</t>
+  </si>
+  <si>
+    <t>Ccompletado</t>
+  </si>
+  <si>
+    <t>Configuracion cursor</t>
+  </si>
+  <si>
+    <t>Se ha modificado configuracion en qlik en relaciona  "Fetcch"</t>
+  </si>
+  <si>
+    <t>Se analizará impacto de mejora</t>
+  </si>
+  <si>
+    <t>Validacion de indices</t>
+  </si>
+  <si>
+    <t>S3 ha compartido una lista de indices a validar</t>
+  </si>
+  <si>
+    <t>NFQ analizará la posibildiad de excluir indices</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -522,12 +549,6 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF1F1F1F"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -549,7 +570,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -560,7 +581,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -904,7 +924,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="43.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="104" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="61.875" customWidth="1"/>
     <col min="6" max="6" width="37.25" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.375" bestFit="1" customWidth="1"/>
   </cols>
@@ -946,7 +966,7 @@
         <v>9</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C2" t="s">
         <v>11</v>
@@ -955,16 +975,16 @@
         <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G2" s="1">
         <v>46223.8125</v>
       </c>
       <c r="H2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="I2" t="s">
         <v>8</v>
@@ -975,10 +995,10 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>105</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>107</v>
       </c>
       <c r="C3" t="s">
         <v>15</v>
@@ -987,16 +1007,16 @@
         <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F3" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="G3" s="1">
         <v>46254</v>
       </c>
       <c r="H3" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="I3" t="s">
         <v>8</v>
@@ -1007,184 +1027,184 @@
     </row>
     <row r="4" spans="1:10" ht="31.5">
       <c r="A4" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C4" t="s">
         <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="E4" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="G4" s="1">
         <v>46259</v>
       </c>
       <c r="H4" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D5" t="s">
+        <v>120</v>
+      </c>
+      <c r="E5" t="s">
+        <v>128</v>
+      </c>
+      <c r="F5" s="5" t="s">
         <v>133</v>
-      </c>
-      <c r="E5" t="s">
-        <v>142</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>145</v>
       </c>
       <c r="G5" s="1">
         <v>46273</v>
       </c>
       <c r="H5" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="31.5">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D6" t="s">
+        <v>120</v>
+      </c>
+      <c r="E6" t="s">
+        <v>130</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>133</v>
-      </c>
-      <c r="E6" t="s">
-        <v>144</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>146</v>
       </c>
       <c r="G6" s="1">
         <v>46273</v>
       </c>
       <c r="H6" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="C7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D7" t="s">
+        <v>120</v>
+      </c>
+      <c r="E7" t="s">
+        <v>132</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>133</v>
-      </c>
-      <c r="E7" t="s">
-        <v>149</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>150</v>
       </c>
       <c r="G7" s="1">
         <v>46274</v>
       </c>
       <c r="H7" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="31.5">
       <c r="A8" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C8" t="s">
         <v>15</v>
       </c>
       <c r="D8" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="E8" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="G8" s="1">
         <v>46258</v>
       </c>
       <c r="H8" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="47.25">
       <c r="A9" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C9" t="s">
         <v>15</v>
       </c>
       <c r="D9" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="E9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G9" s="1">
-        <v>46260</v>
+        <v>46259</v>
       </c>
       <c r="H9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>14</v>
+        <v>105</v>
       </c>
       <c r="C10" t="s">
         <v>15</v>
       </c>
       <c r="D10" t="s">
-        <v>12</v>
+        <v>120</v>
       </c>
       <c r="E10" t="s">
-        <v>131</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="G10" s="2">
+        <v>121</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="G10" s="1">
         <v>46260</v>
       </c>
       <c r="H10" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1249,7 +1269,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="41.625" bestFit="1" customWidth="1"/>
@@ -1290,106 +1310,158 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D2" t="s">
         <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G2" s="1">
         <v>46246</v>
       </c>
       <c r="H2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="31.5">
       <c r="A3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D3" t="s">
         <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="G3" s="1">
         <v>46244</v>
       </c>
       <c r="H3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="B4" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="C4" t="s">
-        <v>97</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s">
         <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>98</v>
-      </c>
-      <c r="F4" t="s">
-        <v>99</v>
-      </c>
-      <c r="G4" t="s">
-        <v>16</v>
+        <v>138</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="G4" s="1">
+        <v>46244</v>
       </c>
       <c r="H4" t="s">
-        <v>100</v>
+        <v>140</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>117</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>107</v>
+        <v>94</v>
+      </c>
+      <c r="B5" t="s">
+        <v>95</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>96</v>
       </c>
       <c r="D5" t="s">
         <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="F5" t="s">
-        <v>128</v>
-      </c>
-      <c r="G5" s="2">
+        <v>141</v>
+      </c>
+      <c r="G5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>115</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" t="s">
+        <v>116</v>
+      </c>
+      <c r="F6" t="s">
+        <v>142</v>
+      </c>
+      <c r="G6" s="2">
         <v>46246</v>
       </c>
-      <c r="H5" t="s">
-        <v>119</v>
+      <c r="H6" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>143</v>
+      </c>
+      <c r="B7" t="s">
+        <v>144</v>
+      </c>
+      <c r="C7" t="s">
+        <v>109</v>
+      </c>
+      <c r="D7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" t="s">
+        <v>116</v>
+      </c>
+      <c r="F7" t="s">
+        <v>146</v>
+      </c>
+      <c r="G7" s="2">
+        <v>46246</v>
+      </c>
+      <c r="H7" t="s">
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -1397,14 +1469,14 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:H1 D4 G4" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:H1 D5 G5" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="13" bestFit="1" customWidth="1"/>
@@ -1445,60 +1517,112 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C2" t="s">
         <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F2" t="s">
-        <v>103</v>
-      </c>
-      <c r="G2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G2" s="1">
+        <v>46258</v>
+      </c>
+      <c r="H2" t="s">
         <v>17</v>
-      </c>
-      <c r="H2" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="B3" t="s">
-        <v>107</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
         <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>121</v>
+        <v>149</v>
       </c>
       <c r="E3" t="s">
-        <v>122</v>
+        <v>150</v>
       </c>
       <c r="F3" t="s">
-        <v>123</v>
+        <v>151</v>
       </c>
       <c r="G3" s="1">
-        <v>46245</v>
+        <v>46280</v>
       </c>
       <c r="H3" t="s">
-        <v>124</v>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D4" t="s">
+        <v>149</v>
+      </c>
+      <c r="E4" t="s">
+        <v>154</v>
+      </c>
+      <c r="F4" t="s">
+        <v>155</v>
+      </c>
+      <c r="G4" s="1">
+        <v>46281</v>
+      </c>
+      <c r="H4" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" t="s">
+        <v>105</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" t="s">
+        <v>149</v>
+      </c>
+      <c r="E5" t="s">
+        <v>157</v>
+      </c>
+      <c r="F5" t="s">
+        <v>158</v>
+      </c>
+      <c r="G5" s="1">
+        <v>46279</v>
+      </c>
+      <c r="H5" t="s">
+        <v>159</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:H1 G2:H2 C2" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:H1 H2 C2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1539,7 +1663,7 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
@@ -1548,24 +1672,24 @@
         <v>15</v>
       </c>
       <c r="D2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" t="s">
         <v>20</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>21</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>22</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>23</v>
-      </c>
-      <c r="H2" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B3" t="s">
         <v>10</v>
@@ -1574,24 +1698,24 @@
         <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" t="s">
         <v>26</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>27</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>28</v>
-      </c>
-      <c r="H3" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s">
         <v>10</v>
@@ -1600,24 +1724,24 @@
         <v>15</v>
       </c>
       <c r="D4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" t="s">
         <v>31</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>32</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>33</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>34</v>
-      </c>
-      <c r="H4" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B5" t="s">
         <v>10</v>
@@ -1629,146 +1753,146 @@
         <v>12</v>
       </c>
       <c r="E5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5" t="s">
         <v>37</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" t="s">
         <v>38</v>
-      </c>
-      <c r="G5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H5" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" t="s">
         <v>40</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>41</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>42</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>43</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
+        <v>43</v>
+      </c>
+      <c r="G6" t="s">
         <v>44</v>
       </c>
-      <c r="F6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>45</v>
-      </c>
-      <c r="H6" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" t="s">
         <v>47</v>
       </c>
-      <c r="B7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>48</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>49</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>50</v>
       </c>
-      <c r="G7" t="s">
-        <v>51</v>
-      </c>
       <c r="H7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C8" t="s">
         <v>12</v>
       </c>
       <c r="D8" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" t="s">
         <v>53</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>54</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>55</v>
       </c>
-      <c r="G8" t="s">
-        <v>56</v>
-      </c>
       <c r="H8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" t="s">
         <v>57</v>
       </c>
-      <c r="B9" t="s">
-        <v>41</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>58</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>59</v>
       </c>
-      <c r="E9" t="s">
-        <v>60</v>
-      </c>
       <c r="F9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C10" t="s">
         <v>12</v>
       </c>
       <c r="D10" t="s">
+        <v>61</v>
+      </c>
+      <c r="E10" t="s">
         <v>62</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
+        <v>62</v>
+      </c>
+      <c r="G10" t="s">
         <v>63</v>
       </c>
-      <c r="F10" t="s">
-        <v>63</v>
-      </c>
-      <c r="G10" t="s">
-        <v>64</v>
-      </c>
       <c r="H10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1776,25 +1900,25 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C11" t="s">
         <v>12</v>
       </c>
       <c r="D11" t="s">
+        <v>64</v>
+      </c>
+      <c r="E11" t="s">
         <v>65</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>66</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>67</v>
       </c>
-      <c r="G11" t="s">
-        <v>68</v>
-      </c>
       <c r="H11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1802,129 +1926,129 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C12" t="s">
         <v>12</v>
       </c>
       <c r="D12" t="s">
+        <v>68</v>
+      </c>
+      <c r="E12" t="s">
         <v>69</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>70</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>71</v>
       </c>
-      <c r="G12" t="s">
-        <v>72</v>
-      </c>
       <c r="H12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
+        <v>72</v>
+      </c>
+      <c r="B13" t="s">
         <v>73</v>
-      </c>
-      <c r="B13" t="s">
-        <v>74</v>
       </c>
       <c r="C13" t="s">
         <v>12</v>
       </c>
       <c r="D13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E13" t="s">
         <v>75</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>76</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
+        <v>63</v>
+      </c>
+      <c r="H13" t="s">
         <v>77</v>
-      </c>
-      <c r="G13" t="s">
-        <v>64</v>
-      </c>
-      <c r="H13" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
+        <v>78</v>
+      </c>
+      <c r="B14" t="s">
         <v>79</v>
-      </c>
-      <c r="B14" t="s">
-        <v>80</v>
       </c>
       <c r="C14" t="s">
         <v>12</v>
       </c>
       <c r="D14" t="s">
+        <v>80</v>
+      </c>
+      <c r="E14" t="s">
         <v>81</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
+        <v>81</v>
+      </c>
+      <c r="G14" t="s">
+        <v>67</v>
+      </c>
+      <c r="H14" t="s">
         <v>82</v>
-      </c>
-      <c r="F14" t="s">
-        <v>82</v>
-      </c>
-      <c r="G14" t="s">
-        <v>68</v>
-      </c>
-      <c r="H14" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
+        <v>83</v>
+      </c>
+      <c r="B15" t="s">
         <v>84</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" t="s">
         <v>85</v>
       </c>
-      <c r="C15" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>86</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
+        <v>86</v>
+      </c>
+      <c r="G15" t="s">
         <v>87</v>
       </c>
-      <c r="F15" t="s">
-        <v>87</v>
-      </c>
-      <c r="G15" t="s">
+      <c r="H15" t="s">
         <v>88</v>
-      </c>
-      <c r="H15" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
+        <v>89</v>
+      </c>
+      <c r="B16" t="s">
+        <v>84</v>
+      </c>
+      <c r="C16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" t="s">
         <v>90</v>
       </c>
-      <c r="B16" t="s">
-        <v>85</v>
-      </c>
-      <c r="C16" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>91</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
+        <v>91</v>
+      </c>
+      <c r="G16" t="s">
         <v>92</v>
       </c>
-      <c r="F16" t="s">
-        <v>92</v>
-      </c>
-      <c r="G16" t="s">
+      <c r="H16" t="s">
         <v>93</v>
-      </c>
-      <c r="H16" t="s">
-        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/dashboard_data_template.xlsx
+++ b/dashboard_data_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marco Pichardo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7133B0E-97B3-48A7-85B7-08A9EA13FEFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33C9D9A8-34A1-42B3-B5D3-84ED33A0DC83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="600" yWindow="-16320" windowWidth="28320" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="600" yWindow="-120" windowWidth="28320" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dbMegara" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="177">
   <si>
     <t>tema</t>
   </si>
@@ -509,13 +509,58 @@
   </si>
   <si>
     <t xml:space="preserve"> S3 internalizará PARA vermeg</t>
+  </si>
+  <si>
+    <t>Estoque RV</t>
+  </si>
+  <si>
+    <t>Estoque Futuros</t>
+  </si>
+  <si>
+    <t>Estoque Fundos</t>
+  </si>
+  <si>
+    <t>Estoque RF</t>
+  </si>
+  <si>
+    <t>Validacion datos</t>
+  </si>
+  <si>
+    <t>En alineacion con Guilherme/Meneses</t>
+  </si>
+  <si>
+    <t>Datos vdiados</t>
+  </si>
+  <si>
+    <t>Datos validados</t>
+  </si>
+  <si>
+    <t>Se alienara con Meneses query de caga</t>
+  </si>
+  <si>
+    <t>ClientInstruction</t>
+  </si>
+  <si>
+    <t>ValoriePosition</t>
+  </si>
+  <si>
+    <t>Vermeg desplegó en PRD sin alineacion previa</t>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>Archivo atascado</t>
+  </si>
+  <si>
+    <t>NFQ validará</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -531,6 +576,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -540,7 +591,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -548,13 +599,32 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -894,14 +964,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="43.875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="94.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -933,7 +1003,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -965,7 +1035,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -997,7 +1067,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -1029,7 +1099,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -1061,7 +1131,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -1093,7 +1163,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -1125,7 +1195,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -1155,6 +1225,84 @@
       </c>
       <c r="J8" t="s">
         <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" t="s">
+        <v>171</v>
+      </c>
+      <c r="F9" t="s">
+        <v>173</v>
+      </c>
+      <c r="G9" s="3">
+        <v>46305</v>
+      </c>
+      <c r="H9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" t="s">
+        <v>172</v>
+      </c>
+      <c r="F10" t="s">
+        <v>173</v>
+      </c>
+      <c r="G10" s="3">
+        <v>46305</v>
+      </c>
+      <c r="H10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" t="s">
+        <v>174</v>
+      </c>
+      <c r="F11" t="s">
+        <v>175</v>
+      </c>
+      <c r="G11" s="3">
+        <v>46305</v>
+      </c>
+      <c r="H11" t="s">
+        <v>176</v>
       </c>
     </row>
   </sheetData>
@@ -1167,10 +1315,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1196,7 +1344,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>35</v>
       </c>
@@ -1222,7 +1370,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>35</v>
       </c>
@@ -1248,7 +1396,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>35</v>
       </c>
@@ -1274,38 +1422,38 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>47</v>
+    <row r="5" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="B5" t="s">
-        <v>48</v>
+        <v>156</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
         <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>49</v>
+        <v>166</v>
       </c>
       <c r="F5" t="s">
-        <v>50</v>
-      </c>
-      <c r="G5" t="s">
-        <v>51</v>
+        <v>168</v>
+      </c>
+      <c r="G5" s="3">
+        <v>46310</v>
       </c>
       <c r="H5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>53</v>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>162</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>156</v>
       </c>
       <c r="C6" t="s">
         <v>17</v>
@@ -1314,51 +1462,155 @@
         <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>54</v>
+        <v>166</v>
       </c>
       <c r="F6" t="s">
-        <v>153</v>
-      </c>
-      <c r="G6" t="s">
-        <v>55</v>
+        <v>169</v>
+      </c>
+      <c r="G6" s="3">
+        <v>46310</v>
       </c>
       <c r="H6" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>56</v>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>163</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>156</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D7" t="s">
         <v>12</v>
       </c>
       <c r="E7" t="s">
+        <v>166</v>
+      </c>
+      <c r="F7" t="s">
+        <v>169</v>
+      </c>
+      <c r="G7" s="3">
+        <v>46310</v>
+      </c>
+      <c r="H7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" t="s">
+        <v>166</v>
+      </c>
+      <c r="F8" t="s">
+        <v>167</v>
+      </c>
+      <c r="G8" s="3">
+        <v>46310</v>
+      </c>
+      <c r="H8" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" t="s">
+        <v>49</v>
+      </c>
+      <c r="F9" t="s">
+        <v>50</v>
+      </c>
+      <c r="G9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H9" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" t="s">
         <v>54</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F10" t="s">
+        <v>153</v>
+      </c>
+      <c r="G10" t="s">
+        <v>55</v>
+      </c>
+      <c r="H10" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11" t="s">
         <v>58</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G11" t="s">
         <v>55</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H11" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="H8" s="1"/>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H12" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:H2 A5:H5 A3:E3 G3:H3 A4:E4 G4:H4 A7:G7 A6:E6 G6" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:H2 A9:H9 A3:E3 G3:H3 A4:E4 G4:H4 A11:G11 A10:E10 G10" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1366,9 +1618,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1394,7 +1646,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>59</v>
       </c>
@@ -1420,7 +1672,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>158</v>
       </c>
@@ -1446,7 +1698,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>64</v>
       </c>
@@ -1483,9 +1735,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:H16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1511,7 +1763,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>69</v>
       </c>
@@ -1537,7 +1789,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>76</v>
       </c>
@@ -1563,7 +1815,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>81</v>
       </c>
@@ -1589,7 +1841,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>87</v>
       </c>
@@ -1615,7 +1867,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>91</v>
       </c>
@@ -1641,7 +1893,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>64</v>
       </c>
@@ -1667,7 +1919,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>102</v>
       </c>
@@ -1693,7 +1945,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>107</v>
       </c>
@@ -1719,7 +1971,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>91</v>
       </c>
@@ -1745,7 +1997,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>115</v>
       </c>
@@ -1771,7 +2023,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>115</v>
       </c>
@@ -1797,7 +2049,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>124</v>
       </c>
@@ -1823,7 +2075,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>130</v>
       </c>
@@ -1849,7 +2101,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>135</v>
       </c>
@@ -1875,7 +2127,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>141</v>
       </c>

--- a/dashboard_data_template.xlsx
+++ b/dashboard_data_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marco Pichardo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33C9D9A8-34A1-42B3-B5D3-84ED33A0DC83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06311E94-0C74-4FF9-98BA-F917DC3E3F84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="600" yWindow="-120" windowWidth="28320" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="600" yWindow="-16320" windowWidth="28320" windowHeight="16440" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dbMegara" sheetId="1" r:id="rId1"/>
@@ -18,12 +18,47 @@
     <sheet name="dbInfra" sheetId="3" r:id="rId3"/>
     <sheet name="dbUAT" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="181">
   <si>
     <t>tema</t>
   </si>
@@ -554,6 +589,18 @@
   </si>
   <si>
     <t>NFQ validará</t>
+  </si>
+  <si>
+    <t>function_meg_sac_pl_cl_patrfut_t</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NFQ / S3 </t>
+  </si>
+  <si>
+    <t>Ajuste en Funcion</t>
+  </si>
+  <si>
+    <t>Ajuste necesario para implmentacion de nuevos campos de DAT_VALUAT, DES_OWNER</t>
   </si>
 </sst>
 </file>
@@ -1734,7 +1781,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2151,6 +2198,33 @@
       </c>
       <c r="H16" t="s">
         <v>145</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>177</v>
+      </c>
+      <c r="B17" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" t="s">
+        <v>178</v>
+      </c>
+      <c r="E17" t="s">
+        <v>179</v>
+      </c>
+      <c r="F17" t="s">
+        <v>180</v>
+      </c>
+      <c r="G17" s="3">
+        <v>46321</v>
+      </c>
+      <c r="H17" t="e" cm="1">
+        <f t="array" ref="H17">- S3 tiene que validar ajustes hechos en UAT</f>
+        <v>#NAME?</v>
       </c>
     </row>
   </sheetData>
